--- a/baseline/data_processing_elements-NHANES13.xlsx
+++ b/baseline/data_processing_elements-NHANES13.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A3BD33-17F0-4861-9EF6-6F49DA17704D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31732D40-270F-4A14-9415-AB17BB2B83CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="1840" windowWidth="19420" windowHeight="10300" xr2:uid="{3161BE6F-2E10-4AFE-B2DF-B65F0CC4B714}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3161BE6F-2E10-4AFE-B2DF-B65F0CC4B714}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="892">
   <si>
     <t>index</t>
   </si>
@@ -3645,11 +3645,6 @@
 Taken prescription medicine, past month</t>
   </si>
   <si>
-    <t>case_when(
-(!BMIWT %in% c(4)) &amp; (! is.na(BMIWT)) ~ 2L; 
-ELSE ~ NA_integer_)</t>
-  </si>
-  <si>
     <t>Non-smokers (never smoked at least 100 cigarettes in life) were coded as 0. The study-specific maximum for Avg # cigarettes/day during past 30 days was 95 cigarettes a day, and the minimum was  1 cigarette a day.</t>
   </si>
   <si>
@@ -3698,6 +3693,15 @@
   <si>
     <t xml:space="preserve">Non-drinkers were coded as 0. The study-specific information was based on responses about alcohol use in the past 12 months. Mean grams of alcohol per standard drink in the United States (14g) was used for calculations. 
 </t>
+  </si>
+  <si>
+    <t>Additional updates following crosschecks.</t>
+  </si>
+  <si>
+    <t>case_when(
+BMIWT == 4 ~ NA_integer_; 
+!is.na(BMIWT) ~ 2L; 
+ELSE ~ NA_integer_)</t>
   </si>
 </sst>
 </file>
@@ -4429,7 +4433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:32" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -4529,7 +4533,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="8" spans="1:32" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -5190,7 +5194,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="5" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" s="5" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -5906,11 +5910,14 @@
       <c r="X30" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="Y30" s="5" t="s">
-        <v>883</v>
+      <c r="Y30" s="7" t="s">
+        <v>891</v>
       </c>
       <c r="Z30" s="5" t="s">
         <v>748</v>
+      </c>
+      <c r="AB30" s="7" t="s">
+        <v>890</v>
       </c>
     </row>
     <row r="31" spans="1:28" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -7215,7 +7222,7 @@
         <v>774</v>
       </c>
       <c r="U54" s="7" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="V54" s="5" t="s">
         <v>466</v>
@@ -7227,7 +7234,7 @@
         <v>492</v>
       </c>
       <c r="Y54" s="7" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="Z54" s="5" t="s">
         <v>670</v>
@@ -7433,10 +7440,10 @@
         <v>397</v>
       </c>
       <c r="L58" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="M58" s="5" t="s">
         <v>886</v>
-      </c>
-      <c r="M58" s="5" t="s">
-        <v>887</v>
       </c>
       <c r="N58" s="5" t="s">
         <v>777</v>
@@ -7448,10 +7455,10 @@
         <v>578</v>
       </c>
       <c r="S58" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="U58" s="7" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="V58" s="5" t="s">
         <v>466</v>
@@ -7463,7 +7470,7 @@
         <v>492</v>
       </c>
       <c r="Y58" s="7" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="Z58" s="5" t="s">
         <v>732</v>
@@ -7575,7 +7582,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="61" spans="1:28" s="5" customFormat="1" ht="135" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" s="5" customFormat="1" ht="120" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>60</v>
       </c>

--- a/baseline/data_processing_elements-NHANES13.xlsx
+++ b/baseline/data_processing_elements-NHANES13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twey\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31732D40-270F-4A14-9415-AB17BB2B83CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C5057E-286F-46C2-89AA-34D4554B35F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3161BE6F-2E10-4AFE-B2DF-B65F0CC4B714}"/>
   </bookViews>
@@ -3700,7 +3700,7 @@
   <si>
     <t>case_when(
 BMIWT == 4 ~ NA_integer_; 
-!is.na(BMIWT) ~ 2L; 
+!is.na(BMXWT) ~ 2L; 
 ELSE ~ NA_integer_)</t>
   </si>
 </sst>
